--- a/resultado_classificacao.xlsx
+++ b/resultado_classificacao.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Atraso em entrega de documentos</t>
+          <t>Sistema legado sem atualizacao de seguranca</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Contribuinte nao entregou declaracao no prazo estipulado</t>
+          <t>Servidor de aplicacao roda versao obsoleta com CVE critico sem plano de correcao</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -476,7 +476,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pode gerar multas e penalidades financeiras para o contribuinte</t>
+          <t>O sistema legado sem atualização de segurança representa vulnerabilidade crítica e risco elevado.</t>
         </is>
       </c>
     </row>
@@ -488,27 +488,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Solicitacao de isencao sem documentacao</t>
+          <t>Contrato sem assinatura digital</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Empresa solicita isencao de ICMS sem anexar documentos obrigatorios</t>
+          <t>Contrato enviado para fornecedor aguarda assinatura digital ha mais de 20 dias</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Juridico</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Medio</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Falta de documentacao obrigatoria pode levar a penalidades e multas</t>
+          <t>Falta de assinatura digital impede a validação legal do contrato</t>
         </is>
       </c>
     </row>
@@ -520,27 +520,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pagamento registrado em duplicidade</t>
+          <t>Fornecedor com CNPJ irregular</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fornecedor registrou mesmo pagamento duas vezes no sistema</t>
+          <t>CNPJ do prestador consta como suspenso no momento da emissao da ordem de servico</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Juridico</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baixo</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Erro de registro duplicado, fácil de identificar e corrigir</t>
+          <t>CNPJ irregular do fornecedor eleva risco de compliance</t>
         </is>
       </c>
     </row>
@@ -552,12 +552,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Acesso nao autorizado ao sistema</t>
+          <t>Acesso de usuario desligado ainda ativo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Usuario tentou acessar modulo restrito sem permissao</t>
+          <t>Colaborador desligado ha 15 dias ainda possui credencial de acesso ativa no sistema</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Baixo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Acesso não autorizado pode comprometer a segurança dos dados e sistemas</t>
+          <t>Usuário desligado ainda possui acesso ativo, risco classificado como Baixo conforme regra.</t>
         </is>
       </c>
     </row>
@@ -584,17 +584,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Contrato vencido sem renovacao</t>
+          <t>Mercadoria transportada sem documentacao</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Contrato com fornecedor expirou sem processo de renovacao iniciado</t>
+          <t>Veiculo interceptado na divisa transportando mercadoria sem nota fiscal ou manifesto</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Juridico</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pode gerar responsabilidades legais e financeiras para a empresa</t>
+          <t>Transporte de mercadoria sem documentação exigida</t>
         </is>
       </c>
     </row>
@@ -616,27 +616,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Erro em calculo de tributo</t>
+          <t>Divergencia entre estoque e sistema</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Calculo de ICMS gerou valor incorreto por parametro desatualizado</t>
+          <t>Inventario identificou sobra de 12 unidades nao registradas no modulo de almoxarifado</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Medio</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Erro no calculo de tributo pode gerar multas e penalidades financeiras</t>
+          <t>Diferença entre estoque e sistema indica falha de controle que pode gerar perdas financeiras</t>
         </is>
       </c>
     </row>
@@ -648,27 +648,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ausencia de servidor em periodo critico</t>
+          <t>Solicitacao de isencao sem documentacao</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Servidor responsavel por entrega ausentou sem substituto designado</t>
+          <t>Empresa solicitou isencao de ICMS sem anexar os documentos comprobatorios obrigatorios</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>Fiscal</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Baixo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Falta de substituto pode causar atrasos ou perda de produtividade</t>
+          <t>Falta de documentação para isenção de ICMS classifica como risco baixo</t>
         </is>
       </c>
     </row>
@@ -680,27 +680,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dado cadastral desatualizado</t>
+          <t>Sistema legado sem atualizacao de seguranca</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CPF do contribuinte com endereco incorreto gerando retorno de correspondencia</t>
+          <t>Sistema critico operando com versao desatualizada exposta a vulnerabilidades conhecidas</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fiscal</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medio</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pode causar atrasos ou perdas de comunicação oficial</t>
+          <t>Sistema legado sem atualização de segurança expõe vulnerabilidades críticas</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rotina de backup nao executou por tres dias consecutivos</t>
+          <t>Job agendado de copia de seguranca falhou silenciosamente sem gerar alerta</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Baixo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Perda de dados críticos pode ocorrer devido à falha no backup</t>
+          <t>Falha em backup de dados está classificada como risco baixo segundo as regras.</t>
         </is>
       </c>
     </row>
@@ -744,27 +744,6107 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Dado cadastral desatualizado</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CPF do contribuinte possui endereco incorreto gerando retorno de correspondencias oficiais</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pedido de isencao tributaria protocolado sem laudo tecnico e certidoes exigidas</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção tributária, classificada como risco baixo segundo as regras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rotina de backup nao foi executada por tres dias consecutivos sem registro de erro</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados está classificada como risco baixo segundo as regras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Prazo processual em risco por falta de monitoramento ativo das movimentacoes do caso</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Falta de acompanhamento judicial coloca o prazo processual em risco</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pagamento registrado em duplicidade</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ordem de pagamento emitida em duplicidade para o mesmo fornecedor e competencia</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Duplicidade de pagamento é classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Acao judicial em andamento sem movimentacao registrada ha mais de 60 dias</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento está na lista de riscos médios</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Divergencia entre estoque e sistema</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Quantidade registrada no sistema diverge do estoque fisico verificado na contagem</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diferença entre estoque físico e registro pode gerar perdas financeiras e falhas de controle</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Processo sem responsavel definido</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Demanda aberta ha 30 dias sem atribuicao de responsavel</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Solicitacao de area de negocio aguarda tratamento sem designacao formal de responsavel</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Gestao</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ausência de responsável formal aumenta risco de falhas e atrasos</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Contrato vencido sem renovacao</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Instrumento contratual encerrou vigencia sem aditivo ou novo processo licitatorio</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Contrato expirou sem renovação, gerando risco de interrupção de serviços</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Processo sem responsavel definido</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Demanda foi aberta ha mais de 30 dias sem atribuicao de responsavel no sistema</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Falta de responsável definido gera atraso e falta de controle</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sistema legado sem atualizacao de seguranca</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sistema critico operando com versao desatualizada exposta a vulnerabilidades conhecidas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Falta de responsabilidade definida pode causar atrasos e ineficiência no processo</t>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Sistema legado crítico sem atualizações expõe vulnerabilidades conhecidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Licenca de software vencida</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Software critico operando com licenca expirada colocando o orgao em risco de penalidade</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Licença de software vencida classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Licenca de software vencida</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Suite de escritorio com licenciamento vencido em uso por setor administrativo ha 45 dias</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Licença de software vencida está listada como risco de baixa gravidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dado sensivel exposto em relatorio</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dashboard compartilhado externamente continha informacoes medicas de servidores</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Exposição de dados sensíveis em relatório externo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ciclo de auditoria interna nao foi realizado no prazo previsto sem registro de justificativa</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa está classificada como risco médio conforme a regra estabelecida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mercadoria transportada sem documentacao</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Transportadora realizou entrega sem documentacao fiscal habilitadora do transito</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Entrega sem documentação fiscal habilitadora gera risco máximo de não conformidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Divergencia entre estoque e sistema</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Saldo contabil de materiais de consumo nao bate com levantamento fisico realizado</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diferença entre estoque e sistema pode gerar perdas financeiras e necessidade de ajustes contábeis</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Empresa solicitou isencao de ICMS sem anexar os documentos comprobatorios obrigatorios</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção de ICMS classifica como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Entrega realizada fora do prazo contratual gerou incidencia de penalidade pecuniaria</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual está na lista de riscos sempre classificados como Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Divergencia entre estoque e sistema</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Inventario identificou sobra de 12 unidades nao registradas no modulo de almoxarifado</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diferença entre estoque e sistema pode gerar perdas financeiras e comprometer o controle interno</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor incorreto</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Valor unitario informado na nota fiscal diverge da tabela de precos homologada</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Valor divergente da tabela homologada caracteriza risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mercadoria transportada sem documentacao</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Transportadora realizou entrega sem documentacao fiscal habilitadora do transito</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Entrega sem documentação fiscal habilitadora gera risco alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Razao social do fornecedor no cadastro diverge do registro atual na Receita Federal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Informação do fornecedor desatualizada pode gerar inconsistências fiscais</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sistema legado sem atualizacao de seguranca</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Aplicacao legada nao recebeu patch de seguranca em mais de seis meses de operacao</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Falha crítica de segurança em sistema legado sem atualizações</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Fornecedor com CNPJ irregular</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Empresa contratada apresenta restricoes cadastrais em consulta ao portal da RFB</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CNPJ irregular indica risco elevado de inadimplência e questões legais</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutencao preventiva</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Servidor fisico nao recebeu manutencao preventiva dentro do cronograma estabelecido</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Classificado como Baixo conforme regra de risco permanente</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pagamento registrado em duplicidade</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sistema processou dois lancamentos identicos para a mesma nota fiscal do fornecedor</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Duplicidade de pagamento é classificada como risco baixo conforme a lista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Atraso em entrega de documentos</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Documentos solicitados pelo fisco nao foram apresentados no prazo de 10 dias uteis</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>O atraso na entrega de documentos ao fisco está classificado como risco médio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fornecedor com CNPJ irregular</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fornecedor ativo no cadastro possui CNPJ com situacao irregular junto a Receita Federal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CNPJ irregular do fornecedor gera alto risco de compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Entrega realizada fora do prazo contratual gerou incidencia de penalidade pecuniaria</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual gera risco alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Contrato vencido sem renovacao</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Fornecedor continuou prestando servico apos vencimento contratual sem formalizacao</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Contrato expirado sem renovação gera risco de não conformidade contratual</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Contrato vencido sem renovacao</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Fornecedor continuou prestando servico apos vencimento contratual sem formalizacao</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Contrato expirado sem renovação gera risco de não conformidade jurídica</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor incorreto</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NF-e emitida com CFOP incorreto alterando a classificacao fiscal da operacao</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Erro na nota fiscal com valor incorreto classifica como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Licenca de software vencida</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ferramenta de monitoramento de rede expirou contrato de suporte sem renovacao aprovada</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Licença de software vencida classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mercadoria transportada sem documentacao</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Veiculo interceptado na divisa transportando mercadoria sem nota fiscal ou manifesto</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Transporte sem documentação gera alta exposição legal e fiscal</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Acesso nao autorizado ao sistema</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Log do sistema registrou acesso indevido a painel administrativo por usuario comum</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Acesso não autorizado ao sistema é classificado como risco alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Contrato vencido sem renovacao</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Instrumento contratual encerrou vigencia sem aditivo ou novo processo licitatorio</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Contrato expirou sem renovação, podendo gerar interrupção ou penalidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor incorreto</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NF-e emitida com CFOP incorreto alterando a classificacao fiscal da operacao</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Erro na nota fiscal com valor incorreto altera a classificação fiscal</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Processo na vara fiscal nao possui advogado responsavel designado para acompanhamento</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Falta de advogado responsável para acompanhamento do processo judicial</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Processo sem responsavel definido</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Solicitacao de area de negocio aguarda tratamento sem designacao formal de responsavel</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Falta de responsável definido gera atrasos e falta de accountability</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Inadimplemento de obrigacao acessoria pelo contratado resultou em aplicacao de multa</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual está listada como risco sempre Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Acesso de usuario desligado ainda ativo</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Conta de ex-funcionario nao foi desativada apos rescisao contratual registrada no RH</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Usuário desligado ainda tem acesso, risco classificado como Baixo conforme regras</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutencao preventiva</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Servidor fisico nao recebeu manutencao preventiva dentro do cronograma estabelecido</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Classificado como Baixo conforme regra de risco permanente</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Auditoria de conformidade nao ocorreu no trimestre previsto sem abertura de excecao</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa está listada como risco médio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Dado sensivel exposto em relatorio</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Dashboard compartilhado externamente continha informacoes medicas de servidores</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Exposição de dados sensíveis em relatório compartilhado externamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Acesso de usuario desligado ainda ativo</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Conta de ex-funcionario nao foi desativada apos rescisao contratual registrada no RH</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Acesso de usuário desligado ainda ativo está classificado como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Revisao periodica de controles internos esta atrasada sem comunicacao formal ao gestor</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa está classificada como risco médio conforme a regra estabelecida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Acesso nao autorizado ao sistema</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tentativa de acesso a base de dados sigilosa registrada por perfil sem autorizacao</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>A tentativa de acesso por perfil não autorizado representa violação direta de segurança.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutencao preventiva</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Desktop de uso critico nao passou por checagem tecnica no periodo recomendado pelo fabricante</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Classificado como Baixo conforme regra de risco permanente</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Empresa solicitou isencao de ICMS sem anexar os documentos comprobatorios obrigatorios</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção de ICMS é classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Ausencia de servidor em periodo critico</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Colaborador chave entrou em licenca durante prazo legal sem formalizar substituicao</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ausência de servidor em período crítico está classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pagamento registrado em duplicidade</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sistema processou dois lancamentos identicos para a mesma nota fiscal do fornecedor</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Duplicidade de pagamento gera pequeno impacto financeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>P062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Instrumento juridico nao foi assinado eletronicamente dentro do prazo regimental</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Falta de assinatura digital aumenta vulnerabilidade e não cumpre requisitos legais</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Razao social do fornecedor no cadastro diverge do registro atual na Receita Federal</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado conforme lista de risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Declaracao fiscal entregue fora do prazo</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Contribuinte protocolou GIA apos vencimento sujeitando-se a multa por atraso</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Entrega fora do prazo gera multa e se enquadra como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Divergencia entre estoque e sistema</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Inventario identificou sobra de 12 unidades nao registradas no modulo de almoxarifado</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Diferença entre estoque e sistema pode gerar perdas financeiras e falhas de controle</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Acesso nao autorizado ao sistema</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Usuario tentou acessar modulo restrito sem possuir permissao de acesso</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Acesso não autorizado ao sistema é classificado como risco alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Contribuinte requereu beneficio fiscal sem apresentar documentacao de habilitacao</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Solicitação de isenção sem documentação gera risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>P068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Divergencia entre estoque e sistema</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Quantidade registrada no sistema diverge do estoque fisico verificado na contagem</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Diferença entre estoque físico e registro pode gerar perdas financeiras e falhas de controle</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>P069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Declaracao fiscal entregue fora do prazo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Contribuinte protocolou GIA apos vencimento sujeitando-se a multa por atraso</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Entrega fora do prazo gera multa e se enquadra como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>P070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Razao social do fornecedor no cadastro diverge do registro atual na Receita Federal</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>P071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor incorreto</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Valor unitario informado na nota fiscal diverge da tabela de precos homologada</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Valor divergente da tabela de preços homologada</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>P072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Acao judicial em andamento sem movimentacao registrada ha mais de 60 dias</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento está na lista de riscos médios</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>P073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Acesso de usuario desligado ainda ativo</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Conta de ex-funcionario nao foi desativada apos rescisao contratual registrada no RH</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Acesso de usuário desligado ainda ativo está na lista de risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>P074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Contrato enviado para fornecedor aguarda assinatura digital ha mais de 20 dias</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Falta de assinatura digital impede a validação legal do contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>P075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor incorreto</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor divergente do contrato firmado entre as partes</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Valor da nota fiscal divergente do contrato, risco classificado como médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>P076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Fornecedor com CNPJ irregular</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Empresa contratada apresenta restricoes cadastrais em consulta ao portal da RFB</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>CNPJ irregular indica risco elevado de inadimplência e questões legais</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>P077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Contrato enviado para fornecedor aguarda assinatura digital ha mais de 20 dias</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Falta de assinatura digital impede a validação legal do contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>P078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Empresa solicitou isencao de ICMS sem anexar os documentos comprobatorios obrigatorios</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção gera risco baixo conforme regras</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>P079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Divergencia entre estoque e sistema</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Inventario identificou sobra de 12 unidades nao registradas no modulo de almoxarifado</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Diferença entre estoque e sistema pode gerar perdas financeiras e comprometer o controle de ativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>P080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Pagamento registrado em duplicidade</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Sistema processou dois lancamentos identicos para a mesma nota fiscal do fornecedor</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Duplicidade de pagamento gera pequeno impacto financeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>P081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Acesso de usuario desligado ainda ativo</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Conta de ex-funcionario nao foi desativada apos rescisao contratual registrada no RH</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Usuário desligado ainda possui acesso ao sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>P082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Contrato vencido sem renovacao</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Fornecedor continuou prestando servico apos vencimento contratual sem formalizacao</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Contrato vencido sem renovação gera risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>P083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Contribuinte requereu beneficio fiscal sem apresentar documentacao de habilitacao</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>P084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Job agendado de copia de seguranca falhou silenciosamente sem gerar alerta</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Backup falhou silenciosamente sem gerar alerta</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>P085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Contrato vencido sem renovacao</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Fornecedor continuou prestando servico apos vencimento contratual sem formalizacao</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Contrato expirado sem renovação aumenta risco de não conformidade jurídica</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>P086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Fornecedor com CNPJ irregular</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Fornecedor ativo no cadastro possui CNPJ com situacao irregular junto a Receita Federal</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>CNPJ irregular do fornecedor gera risco alto de não conformidade legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>P087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Processo sem responsavel definido</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Solicitacao de area de negocio aguarda tratamento sem designacao formal de responsavel</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Falta de responsável pode atrasar decisões</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>P088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Revisao periodica de controles internos esta atrasada sem comunicacao formal ao gestor</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa está classificada como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>P089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Erro em calculo de tributo</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Aliquota aplicada na apuracao diverge da tabela vigente publicada em diario oficial</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>O erro de cálculo de tributo está listado como risco sempre médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>P090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor incorreto</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor divergente do contrato firmado entre as partes</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Valor da nota fiscal divergente do contrato, risco classificado como médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>P091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor incorreto</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Valor unitario informado na nota fiscal diverge da tabela de precos homologada</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Valor divergente da tabela de preços homologada</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>P092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Contrato enviado para fornecedor aguarda assinatura digital ha mais de 20 dias</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital está pendente há mais de 20 dias, conforme critério de risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>P093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Licenca de software vencida</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Suite de escritorio com licenciamento vencido em uso por setor administrativo ha 45 dias</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Licença vencida está listada como risco sempre baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>P094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Prazo processual em risco por falta de monitoramento ativo das movimentacoes do caso</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Falta de acompanhamento judicial coloca o prazo processual em risco</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>P095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Fornecedor com CNPJ irregular</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Fornecedor ativo no cadastro possui CNPJ com situacao irregular junto a Receita Federal</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CNPJ irregular do fornecedor gera risco alto de não conformidade legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>P096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Aditivo contratual encontra-se pendente de assinatura digital por ambas as partes</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Falta de assinatura digital no aditivo aumenta risco de validade e conformidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>P097</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Fornecedor descumpriu clausula contratual sujeitando o orgao a pagamento de multa</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual está na lista de risco sempre Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>P098</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Fornecedor com CNPJ irregular</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Fornecedor ativo no cadastro possui CNPJ com situacao irregular junto a Receita Federal</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>CNPJ irregular do fornecedor gera risco alto de não conformidade legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>P099</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor incorreto</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Valor unitario informado na nota fiscal diverge da tabela de precos homologada</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Valor divergente da tabela homologada gera risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>P100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Erro em calculo de tributo</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Aliquota aplicada na apuracao diverge da tabela vigente publicada em diario oficial</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>O erro de cálculo de tributo está listado como risco sempre médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>P101</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Acesso de usuario desligado ainda ativo</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Login de prestador encerrado continua com permissao de leitura em repositorio interno</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Usuário desligado ainda possui acesso ativo, classificado como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>P102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Acesso nao autorizado ao sistema</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Log do sistema registrou acesso indevido a painel administrativo por usuario comum</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Acesso não autorizado ao sistema é classificado como risco alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>P103</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Erro em calculo de tributo</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Calculo de ICMS gerou valor incorreto devido a parametro desatualizado no sistema</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Erro de cálculo de tributo classificado como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>P104</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Divergencia entre estoque e sistema</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Inventario identificou sobra de 12 unidades nao registradas no modulo de almoxarifado</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Inconsistência de estoque pode gerar perdas financeiras</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>P105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Acao judicial em andamento sem movimentacao registrada ha mais de 60 dias</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento está classificado como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>P106</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Acesso de usuario desligado ainda ativo</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Login de prestador encerrado continua com permissao de leitura em repositorio interno</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Acesso de usuário desligado ainda ativo está na lista de riscos sempre classificados como Baixo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>P107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Rotina de backup nao foi executada por tres dias consecutivos sem registro de erro</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Falha de backup classificada como risco baixo conforme regras</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>P108</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Servidor sem treinamento obrigatorio</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Servidor publico nao concluiu capacitacao obrigatoria de compliance no ciclo vigente</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Servidor público não concluiu a capacitação obrigatória de compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>P109</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Divergencia entre estoque e sistema</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Inventario identificou sobra de 12 unidades nao registradas no modulo de almoxarifado</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Diferença entre estoque físico e registro pode gerar perdas financeiras</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>P110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Pedido de isencao tributaria protocolado sem laudo tecnico e certidoes exigidas</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção tributária, classificada como risco baixo conforme regras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>P111</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Fornecedor descumpriu clausula contratual sujeitando o orgao a pagamento de multa</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual está na lista de risco sempre Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>P112</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Prazo processual em risco por falta de monitoramento ativo das movimentacoes do caso</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Falta de acompanhamento judicial coloca o prazo processual em risco</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>P113</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Prazo processual em risco por falta de monitoramento ativo das movimentacoes do caso</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Falta de acompanhamento judicial coloca o prazo processual em risco</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>P114</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Contribuinte requereu beneficio fiscal sem apresentar documentacao de habilitacao</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>P115</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor incorreto</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>NF-e emitida com CFOP incorreto alterando a classificacao fiscal da operacao</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Erro na nota fiscal com valor incorreto altera a classificação fiscal</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>P116</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Job agendado de copia de seguranca falhou silenciosamente sem gerar alerta</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados está classificada como risco baixo conforme a lista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>P117</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Declaracao fiscal entregue fora do prazo</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Empresa entregou declaracao de apuracao fiscal apos o encerramento do prazo legal</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Entrega fora do prazo está classificada como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>P118</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Dado sensivel exposto em relatorio</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Exportacao de planilha incluiu CPFs e rendimentos de contribuintes sem anonimizacao</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Exposição de CPFs e rendimentos configura risco crítico de privacidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>P119</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Fornecedor com CNPJ irregular</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Empresa contratada apresenta restricoes cadastrais em consulta ao portal da RFB</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>CNPJ irregular indica risco de inadimplência e questões legais</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>P120</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Contrato enviado para fornecedor aguarda assinatura digital ha mais de 20 dias</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital está pendente há mais de 20 dias, conforme critério de risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>P121</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Pagamento registrado em duplicidade</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Fornecedor registrou o mesmo pagamento duas vezes no sistema financeiro</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Duplicidade de pagamento é classificada como risco baixo conforme a lista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>P122</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Empresa solicitou isencao de ICMS sem anexar os documentos comprobatorios obrigatorios</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção de ICMS classifica como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>P123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Dado sensivel exposto em relatorio</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Relatorio gerado pelo sistema expos dados pessoais sensiveis sem mascara de protecao</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Exposição de dados pessoais sensíveis sem máscara de proteção</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>P124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Fornecedor com CNPJ irregular</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CNPJ do prestador consta como suspenso no momento da emissao da ordem de servico</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>CNPJ irregular do fornecedor eleva risco de compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>P125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Inadimplemento de obrigacao acessoria pelo contratado resultou em aplicacao de multa</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual está listada como risco sempre Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>P126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutencao preventiva</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Nobreak do datacenter esta fora do ciclo de revisao preventiva ha dois trimestres</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Classificado como Baixo conforme regra de equipamento sem manutenção preventiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>P127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutencao preventiva</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Nobreak do datacenter esta fora do ciclo de revisao preventiva ha dois trimestres</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutenção preventiva está classificado como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>P128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Pagamento registrado em duplicidade</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Sistema processou dois lancamentos identicos para a mesma nota fiscal do fornecedor</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Duplicidade de pagamento é classificado como risco baixo segundo as regras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>P129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Dado sensivel exposto em relatorio</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Exportacao de planilha incluiu CPFs e rendimentos de contribuintes sem anonimizacao</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Exposição de CPFs e rendimentos configura risco crítico de privacidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>P130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CPF do contribuinte possui endereco incorreto gerando retorno de correspondencias oficiais</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado gera correspondências incorretas</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>P131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Erro em calculo de tributo</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Sistema calculou base de reducao de forma equivocada gerando recolhimento a menor</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Erro em cálculo de tributo está listado como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>P132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Contribuinte requereu beneficio fiscal sem apresentar documentacao de habilitacao</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Classificado como baixo conforme regra de solicitação de isenção sem documentação</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>P133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Backup do banco de dados nao foi validado apos execucao resultando em arquivo corrompido</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados está classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>P134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Razao social do fornecedor no cadastro diverge do registro atual na Receita Federal</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Informação do fornecedor desatualizada pode gerar inconsistências fiscais</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>P135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Erro em calculo de tributo</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Sistema calculou base de reducao de forma equivocada gerando recolhimento a menor</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Erro em cálculo de tributo está listado como risco sempre Médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>P136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Declaracao fiscal entregue fora do prazo</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Contribuinte protocolou GIA apos vencimento sujeitando-se a multa por atraso</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Entregue fora do prazo gera multa por atraso</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>P137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Fornecedor com CNPJ irregular</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Empresa contratada apresenta restricoes cadastrais em consulta ao portal da RFB</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>CNPJ irregular indica risco de inadimplência e questões legais</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>P138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Servidor sem treinamento obrigatorio</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Colaborador nao realizou treinamento de seguranca da informacao dentro do prazo exigido</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Treinamento obrigatório não realizado, classificado como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>P139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Dado sensivel exposto em relatorio</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Relatorio gerado pelo sistema expos dados pessoais sensiveis sem mascara de protecao</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Exposição de dados pessoais sensíveis sem máscara representa risco crítico de violação de privacidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>P140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Contrato vencido sem renovacao</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Instrumento contratual encerrou vigencia sem aditivo ou novo processo licitatorio</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>O contrato expirou sem renovação, configurando risco médio conforme a classificação estabelecida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>P141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Sistema legado sem atualizacao de seguranca</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Sistema critico operando com versao desatualizada exposta a vulnerabilidades conhecidas</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Sistema crítico legado sem patches expõe vulnerabilidades conhecidas</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>P142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CPF do contribuinte possui endereco incorreto gerando retorno de correspondencias oficiais</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado gera correspondências incorretas, classificado como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>P143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Backup do banco de dados nao foi validado apos execucao resultando em arquivo corrompido</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados está classificada como risco baixo conforme a lista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>P144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Dado sensivel exposto em relatorio</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Exportacao de planilha incluiu CPFs e rendimentos de contribuintes sem anonimizacao</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Exposição de CPFs e rendimentos configura risco crítico de privacidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>P145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Auditoria de conformidade nao ocorreu no trimestre previsto sem abertura de excecao</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Atraso na auditoria sem justificativa eleva o risco para médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>P146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Servidor sem treinamento obrigatorio</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Funcionario em funcao critica nao possui certificacao interna de privacidade de dados</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Falta de certificação interna de privacidade para funcionário em função crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>P147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Pedido de isencao tributaria protocolado sem laudo tecnico e certidoes exigidas</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção tributária</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>P148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Sistema legado sem atualizacao de seguranca</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Aplicacao legada nao recebeu patch de seguranca em mais de seis meses de operacao</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Falha crítica de segurança em sistema legado sem atualizações</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>P149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Processo sem responsavel definido</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Solicitacao de area de negocio aguarda tratamento sem designacao formal de responsavel</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Falta de responsável definido gera atrasos e falta de accountability</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>P150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Processo na vara fiscal nao possui advogado responsavel designado para acompanhamento</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento está na lista de risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>P151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor incorreto</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>NF-e emitida com CFOP incorreto alterando a classificacao fiscal da operacao</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Classificado como risco médio conforme regra de nota fiscal com valor incorreto</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>P152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Contrato vencido sem renovacao</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Instrumento contratual encerrou vigencia sem aditivo ou novo processo licitatorio</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Contrato expirou sem renovação, risco de interrupção de serviços</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>P153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Atraso em entrega de documentos</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Documentos solicitados pelo fisco nao foram apresentados no prazo de 10 dias uteis</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Atraso na entrega de documentos fiscais é classificado como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>P154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Job agendado de copia de seguranca falhou silenciosamente sem gerar alerta</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados está classificada como risco baixo conforme a lista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>P155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Contrato vencido sem renovacao</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Contrato com fornecedor expirou sem que o processo de renovacao fosse iniciado</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Contrato expirou sem iniciar renovação</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>P156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Auditoria de conformidade nao ocorreu no trimestre previsto sem abertura de excecao</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa está listada como risco médio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>P157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Processo sem responsavel definido</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Chamado critico permanece sem dono apos redistribuicao de equipe nao comunicada</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Ausência de responsável pode atrasar a solução do chamado crítico</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>P158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Atraso em entrega de documentos</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Contribuinte nao entregou declaracao fiscal dentro do prazo estipulado pela legislacao</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Atraso na entrega de declaração fiscal é classificado como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>P159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Job agendado de copia de seguranca falhou silenciosamente sem gerar alerta</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Backup falhou silenciosamente sem alerta, comprometendo a recuperação de dados</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>P160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Contrato vencido sem renovacao</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Fornecedor continuou prestando servico apos vencimento contratual sem formalizacao</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Contrato expirado sem renovação gera risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>P161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor incorreto</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Nota fiscal emitida com valor divergente do contrato firmado entre as partes</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Valor divergente do contrato gera risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>P162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Aditivo contratual encontra-se pendente de assinatura digital por ambas as partes</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Falta de assinatura digital no aditivo aumenta risco de validade e conformidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>P163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Sistema legado sem atualizacao de seguranca</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Aplicacao legada nao recebeu patch de seguranca em mais de seis meses de operacao</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Falta de patches deixa o sistema vulnerável a ataques</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>P164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutencao preventiva</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Desktop de uso critico nao passou por checagem tecnica no periodo recomendado pelo fabricante</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Equipamento crítico sem manutenção preventiva aumenta risco de falha</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>P165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Licenca de software vencida</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Ferramenta de monitoramento de rede expirou contrato de suporte sem renovacao aprovada</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Licença expirou sem renovação, risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>P166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Acesso nao autorizado ao sistema</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Usuario tentou acessar modulo restrito sem possuir permissao de acesso</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Acesso não autorizado ao sistema é classificado como risco alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>P167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Acesso nao autorizado ao sistema</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Usuario tentou acessar modulo restrito sem possuir permissao de acesso</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Acesso não autorizado ao sistema</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>P168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Acesso nao autorizado ao sistema</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Tentativa de acesso a base de dados sigilosa registrada por perfil sem autorizacao</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>A tentativa de acesso por perfil não autorizado representa violação direta de segurança.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>P169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Pedido de isencao tributaria protocolado sem laudo tecnico e certidoes exigidas</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção tributária, classificado como risco baixo conforme regras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>P170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Rotina de backup nao foi executada por tres dias consecutivos sem registro de erro</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Falha em backup de dados está classificada como risco baixo conforme a lista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>P171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Pagamento registrado em duplicidade</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Fornecedor registrou o mesmo pagamento duas vezes no sistema financeiro</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Duplicidade de pagamento é classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>P172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Licenca de software vencida</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Suite de escritorio com licenciamento vencido em uso por setor administrativo ha 45 dias</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Licença de software vencida há 45 dias, classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>P173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Sistema legado sem atualizacao de seguranca</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Sistema critico operando com versao desatualizada exposta a vulnerabilidades conhecidas</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Sistema legado sem atualização de segurança expõe vulnerabilidades críticas</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>P174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Acesso nao autorizado ao sistema</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Log do sistema registrou acesso indevido a painel administrativo por usuario comum</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Acesso indevido a painel administrativo por usuário comum</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>P175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Declaracao fiscal entregue fora do prazo</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Empresa entregou declaracao de apuracao fiscal apos o encerramento do prazo legal</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Entrega fora do prazo é classificada como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>P176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Aditivo contratual encontra-se pendente de assinatura digital por ambas as partes</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Falta de assinatura digital no aditivo aumenta risco de validade e conformidade</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>P177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CPF do contribuinte possui endereco incorreto gerando retorno de correspondencias oficiais</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Dado cadastral desatualizado gera correspondências oficiais incorretas</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>P178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutencao preventiva</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Desktop de uso critico nao passou por checagem tecnica no periodo recomendado pelo fabricante</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Falta de manutenção preventiva em equipamento crítico é classificado como risco baixo segundo as regras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>P179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Sistema legado sem atualizacao de seguranca</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Sistema critico operando com versao desatualizada exposta a vulnerabilidades conhecidas</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Sistema legado sem atualização de segurança expõe vulnerabilidades críticas</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>P180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Acesso nao autorizado ao sistema</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Log do sistema registrou acesso indevido a painel administrativo por usuario comum</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Acesso não autorizado ao sistema é classificado como risco alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>P181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Pedido de isencao tributaria protocolado sem laudo tecnico e certidoes exigidas</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção tributária, classificada como risco baixo conforme regras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>P182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Pedido de isencao tributaria protocolado sem laudo tecnico e certidoes exigidas</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção tributária, classificado como risco baixo conforme regras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>P183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Servidor sem treinamento obrigatorio</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Funcionario em funcao critica nao possui certificacao interna de privacidade de dados</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Falta de treinamento obrigatório para servidor em função crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>P184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Ausencia de servidor em periodo critico</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Equipe ficou sem responsavel tecnico durante auditoria externa por ausencia nao planejada</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Classificado como Baixo por estar na lista de risco sempre baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>P185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Atraso em entrega de documentos</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Contribuinte nao entregou declaracao fiscal dentro do prazo estipulado pela legislacao</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Atraso na entrega de documentos fiscais é classificado como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>P186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Revisao periodica de controles internos esta atrasada sem comunicacao formal ao gestor</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa está classificada como risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>P187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Pagamento registrado em duplicidade</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Ordem de pagamento emitida em duplicidade para o mesmo fornecedor e competencia</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Duplicidade de pagamento é classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>P188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Licenca de software vencida</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ferramenta de monitoramento de rede expirou contrato de suporte sem renovacao aprovada</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Licença de software vencida, risco baixo conforme regra</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>P189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Solicitacao de isencao sem documentacao</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Empresa solicitou isencao de ICMS sem anexar os documentos comprobatorios obrigatorios</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Fiscal</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Falta de documentação para isenção de ICMS é classificada como risco baixo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>P190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutencao preventiva</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Nobreak do datacenter esta fora do ciclo de revisao preventiva ha dois trimestres</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutenção preventiva está fora do ciclo, risco classificado como baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>P191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Divergencia entre estoque e sistema</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Quantidade registrada no sistema diverge do estoque fisico verificado na contagem</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Diferença entre estoque físico e registro no sistema pode gerar perdas financeiras e erros contábeis</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>P192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Entrega realizada fora do prazo contratual gerou incidencia de penalidade pecuniaria</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Multa por descumprimento contratual está na lista de risco sempre Alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>P193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Servidor sem treinamento obrigatorio</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Funcionario em funcao critica nao possui certificacao interna de privacidade de dados</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>RH</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Falta de treinamento obrigatório classificada como risco baixo</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>P194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Acao judicial em andamento sem movimentacao registrada ha mais de 60 dias</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Processo judicial sem acompanhamento está na lista de risco médio</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>P195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Ciclo de auditoria interna nao foi realizado no prazo previsto sem registro de justificativa</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Gestao</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Auditoria atrasada sem justificativa está classificada como risco médio conforme a regra estabelecida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>P196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Pagamento registrado em duplicidade</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Ordem de pagamento emitida em duplicidade para o mesmo fornecedor e competencia</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Duplicidade de pagamento gera pequeno impacto financeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>P197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Divergencia entre estoque e sistema</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Saldo contabil de materiais de consumo nao bate com levantamento fisico realizado</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Financeiro</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Diferença entre estoque e sistema pode gerar perdas financeiras e necessidade de ajuste contábil</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>P198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Contrato enviado para fornecedor aguarda assinatura digital ha mais de 20 dias</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Contrato sem assinatura digital está pendente há mais de 20 dias, configurando risco médio conforme regra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>P199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Dado sensivel exposto em relatorio</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Exportacao de planilha incluiu CPFs e rendimentos de contribuintes sem anonimizacao</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Exposição de CPFs e rendimentos sem anonimização</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>P200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutencao preventiva</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Nobreak do datacenter esta fora do ciclo de revisao preventiva ha dois trimestres</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Baixo</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Equipamento sem manutenção preventiva está classificado como risco baixo.</t>
         </is>
       </c>
     </row>
